--- a/Mass_update_AQUA/mass_update_AQUA_quantity_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_quantity_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0RKf00000ExsRt</t>
+          <t>a0RQQ00000Lar3J</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -466,14 +466,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10330_AQU001_2</t>
+          <t>12490_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0RKf00000ExtwE</t>
+          <t>a0RQQ00000LcAwj</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,14 +486,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11261_AQU001_2</t>
+          <t>16643_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0RQQ00000Hu4bp</t>
+          <t>a0RQQ00000LPbl3</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -506,14 +506,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11429_AQU001_2</t>
+          <t>17010_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0RQQ00000KoXi1</t>
+          <t>a0RQQ00000LPaNZ</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -521,19 +521,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AQUA</t>
+          <t>AQUA SOFTWARE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12269_AQU001_2</t>
+          <t>19677_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0RKf00000Exrij</t>
+          <t>a0RQQ00000LeIOj</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,14 +546,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12569_AQU001_2</t>
+          <t>30004475_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0RKf00000ExtxL</t>
+          <t>a0RQQ00000LPb0H</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13120_AQU001_2</t>
+          <t>30005408_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0RQQ00000Jbaxe</t>
+          <t>a0RQQ00000LPak9</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -586,14 +586,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13306_AQU001_2</t>
+          <t>30006827_AQU001_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0RQQ00000J30F4</t>
+          <t>a0RQQ00000LPax3</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -606,127 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13316_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>a0RQQ00000K1rpx</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>14837_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>a0RQQ00000IpOdp</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>18389_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>a0RQQ00000KouwL</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>18451_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>a0RKf00000Exq8w</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>21007_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>a0RQQ00000IJCj3</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>30000578_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>a0RQQ00000HXF4v</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>30000847_AQU001_2</t>
+          <t>30007076_AQU001_2</t>
         </is>
       </c>
     </row>

--- a/Mass_update_AQUA/mass_update_AQUA_quantity_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_quantity_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,166 +450,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>a0RQQ00000Lar3J</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12490_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LcAwj</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16643_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPbl3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>17010_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPaNZ</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>19677_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LeIOj</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>30004475_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPb0H</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>30005408_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPak9</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>30006827_AQU001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPax3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AQUA SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>30007076_AQU001_2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
